--- a/tests/samples/national_ids.xlsx
+++ b/tests/samples/national_ids.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Projects\contacts manager\tests\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56C55199-8732-4E79-9F95-888913774C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2113D351-0110-4182-B99A-91084213543B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{9A1768AA-FB91-4BC8-BA7B-254D9C5E4BAD}"/>
+    <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7360" xr2:uid="{DEB85169-D641-4313-83E6-FA6635344BE8}"/>
   </bookViews>
   <sheets>
     <sheet name="بيانات" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
     <t>سمير عبد الله حسن</t>
   </si>
   <si>
-    <t>29805151234567</t>
+    <t>29805150012345</t>
   </si>
   <si>
     <t>الصف الأول</t>
@@ -57,7 +57,7 @@
     <t>نادية فؤاد الشريف</t>
   </si>
   <si>
-    <t>30112201234568</t>
+    <t>30112200012346</t>
   </si>
   <si>
     <t>ملاحظة عادية</t>
@@ -66,7 +66,7 @@
     <t>رمضان علي محمود</t>
   </si>
   <si>
-    <t>27703101234569</t>
+    <t>27703100012347</t>
   </si>
 </sst>
 </file>
@@ -418,7 +418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B3B7DC3-49DE-4E31-ACA5-5C40E390EFE5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E93645F4-3C57-4BAB-B750-DE16F09E48AD}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -459,7 +459,7 @@
         <v>1005551234</v>
       </c>
       <c r="E2">
-        <v>28809091234561</v>
+        <v>28809090012341</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1005551236</v>
       </c>
       <c r="E4">
-        <v>29001011234562</v>
+        <v>29001010012342</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
